--- a/data/trending_integrated_20261019_10.xlsx
+++ b/data/trending_integrated_20261019_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G2" t="n">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>19500525168</v>
+        <v>19656317416</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급 계약 체결. 국민연금, 미래에셋, 신한, 키움 등 주요 기관 투자자들의 매수세 유입 확인.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급 뉴스 확인. 외인 및 국민연금 순매수 동향 포착.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스페이스X', '강관', '납품']</t>
+          <t>['스페이스X', '공급 계약', '외인 매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9490</v>
+        <v>9340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.31%</t>
+          <t>'+10.53%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -696,13 +696,13 @@
         <v>9880</v>
       </c>
       <c r="M3" t="n">
-        <v>9430</v>
+        <v>9320</v>
       </c>
       <c r="N3" t="n">
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>15206038445</v>
+        <v>16283811945</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -711,23 +711,23 @@
         <v>5390</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-327000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>명신산업, 테슬라 로드스터 수혜주로 부각되며 전체 매출의 70%를 테슬라에 납품. 공매도 및 자사주 매입 관련 언급.</t>
+          <t>명신산업, 테슬라 로드스터 관련 수혜 기대감. 공매도 및 프로그램 매매 동향 혼재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['테슬라', '로드스터', '납품']</t>
+          <t>['테슬라', '로드스터', '공매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9070</v>
+        <v>170700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+2.09%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.02</v>
+        <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="H4" t="n">
-        <v>1.74</v>
+        <v>75.02</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9010</v>
+        <v>167200</v>
       </c>
       <c r="K4" t="n">
-        <v>8810</v>
+        <v>159600</v>
       </c>
       <c r="L4" t="n">
-        <v>9500</v>
+        <v>175500</v>
       </c>
       <c r="M4" t="n">
-        <v>8510</v>
+        <v>159200</v>
       </c>
       <c r="N4" t="n">
-        <v>0.72</v>
+        <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>74911150680</v>
+        <v>293823757850</v>
       </c>
       <c r="P4" t="n">
-        <v>9500</v>
+        <v>243500</v>
       </c>
       <c r="Q4" t="n">
-        <v>2270</v>
+        <v>71000</v>
       </c>
       <c r="R4" t="n">
-        <v>-197000</v>
+        <v>133000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-31000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HT로보틱스, 로봇주로서 시장 관심 집중. 연말 주도주 가능성 및 기관/외인 수급 관련 기대감 형성.</t>
+          <t>삼성전자우, 주문 실수 및 급등락 발생. 시장 참가자들 사이에서 혼란과 관망세 나타남.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇주', '수급', '연말']</t>
+          <t>['주문 실수', '급등락', '관망세']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>213250</v>
+        <v>215750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-1.04%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="G5" t="n">
-        <v>1397</v>
+        <v>1430</v>
       </c>
       <c r="H5" t="n">
         <v>45.99</v>
@@ -886,7 +886,7 @@
         <v>45.98</v>
       </c>
       <c r="O5" t="n">
-        <v>1041584634750</v>
+        <v>1131522988250</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자, CXMT와 기술 격차 관련 시장 우려 과도하다는 뉴스 인용. 개인 매도세 속 외인 순매수 관찰.</t>
+          <t>삼성전자, 주가 하락 속 개인 매도 및 외인 저가 매수세 포착. 호실적 기대감 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['CXMT', '기술 격차', '외인']</t>
+          <t>['외인 매수', '호실적', '저가 매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14390</v>
+        <v>14590</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-2.31%</t>
+          <t>'-0.95%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
         <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="H6" t="n">
         <v>9.699999999999999</v>
@@ -978,7 +978,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>12066689105</v>
+        <v>12824684955</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설, 주가조작 및 뱅크런 관련 정치적 이슈 언급. 외인 보유율 관련 언급 있으나 구체적 근거 부족.</t>
+          <t>대우건설, 잦은 수주 발표에도 불구하고 주가 하락세 지속. 주가 조작 및 외인 보유율 관련 의혹 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가조작', '뱅크런', '외인보유율']</t>
+          <t>['수주', '주가 하락', '주가 조작']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,90 +1023,182 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1221000</v>
+        <v>8830</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-4.01%</t>
+          <t>'-2.00%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.03</v>
+        <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>495</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>1293</v>
+        <v>92</v>
       </c>
       <c r="H7" t="n">
-        <v>48.82</v>
+        <v>1.74</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1272000</v>
+        <v>9010</v>
       </c>
       <c r="K7" t="n">
-        <v>1212000</v>
+        <v>8810</v>
       </c>
       <c r="L7" t="n">
-        <v>1264000</v>
+        <v>9500</v>
       </c>
       <c r="M7" t="n">
-        <v>1208000</v>
+        <v>8510</v>
       </c>
       <c r="N7" t="n">
-        <v>48.85</v>
+        <v>0.72</v>
       </c>
       <c r="O7" t="n">
-        <v>1360063597500</v>
+        <v>79159331000</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>9500</v>
       </c>
       <c r="Q7" t="n">
-        <v>465500</v>
+        <v>2270</v>
       </c>
       <c r="R7" t="n">
-        <v>73000</v>
+        <v>-197000</v>
       </c>
       <c r="S7" t="n">
-        <v>87000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 우회 상장 철회 요구 및 정치적 이슈 연관성 언급. 일부 투자자 손실 및 부정적 전망 제기.</t>
+          <t>HT로보틱스, 로봇주 강세 속 관심 집중. 향후 주도주 가능성 및 자금 유입 여부 주목.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['로봇주', '주도주', '자금 유입']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>396300</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1243000</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-2.28%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E8" t="n">
+        <v>800</v>
+      </c>
+      <c r="F8" t="n">
+        <v>486</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1283</v>
+      </c>
+      <c r="H8" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1272000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1212000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1264000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1208000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1510628646000</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>465500</v>
+      </c>
+      <c r="R8" t="n">
+        <v>73000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>87000</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 솔리다임 우회 상장 이슈로 인한 부정적 여론 형성. 주가 하락 및 경영진 비판.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
         <v>0.2</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>['솔리다임', '우회상장', '정치']</t>
-        </is>
-      </c>
-      <c r="X7" t="n">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['솔리다임', '우회상장', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
         <v>12</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261019_10.xlsx
+++ b/data/trending_integrated_20261019_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
         <v>59</v>
       </c>
       <c r="G2" t="n">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>19656317416</v>
+        <v>19801112996</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9340</v>
+        <v>9430</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.53%</t>
+          <t>'+11.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -696,13 +696,13 @@
         <v>9880</v>
       </c>
       <c r="M3" t="n">
-        <v>9320</v>
+        <v>9300</v>
       </c>
       <c r="N3" t="n">
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>16283811945</v>
+        <v>17262013215</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>명신산업, 테슬라 로드스터 관련 수혜 기대감. 공매도 및 프로그램 매매 동향 혼재.</t>
+          <t>테슬라 로드스터 수혜주로 언급되며 급등 기대감 존재. 자사주 매입 공시와 함께 주가 상승 가능성 제기.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['테슬라', '로드스터', '공매도']</t>
+          <t>['테슬라', '로드스터', '자사주매입']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170700</v>
+        <v>173900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.09%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>293823757850</v>
+        <v>317381665500</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성전자우, 주문 실수 및 급등락 발생. 시장 참가자들 사이에서 혼란과 관망세 나타남.</t>
+          <t>주문 실수로 인한 혼란 속에서 반등 기대감 형성. 시장 전반의 불안정성과 개인투자자 혼조세.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주문 실수', '급등락', '관망세']</t>
+          <t>['우선주', '호가창', '시장가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>215750</v>
+        <v>219500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+1.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="G5" t="n">
-        <v>1430</v>
+        <v>1347</v>
       </c>
       <c r="H5" t="n">
         <v>45.99</v>
@@ -877,7 +877,7 @@
         <v>207000</v>
       </c>
       <c r="L5" t="n">
-        <v>216000</v>
+        <v>219500</v>
       </c>
       <c r="M5" t="n">
         <v>206500</v>
@@ -886,7 +886,7 @@
         <v>45.98</v>
       </c>
       <c r="O5" t="n">
-        <v>1131522988250</v>
+        <v>1261626249000</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자, 주가 하락 속 개인 매도 및 외인 저가 매수세 포착. 호실적 기대감 존재.</t>
+          <t>외인 매수에 따른 상승 기대감과 호실적 언급. 다만, 감정적 표현이 많아 객관적 근거는 부족.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외인 매수', '호실적', '저가 매수']</t>
+          <t>['호실적', '외인매수', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14590</v>
+        <v>15090</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.95%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G6" t="n">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="H6" t="n">
-        <v>9.699999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14730</v>
+        <v>14950</v>
       </c>
       <c r="K6" t="n">
-        <v>14500</v>
+        <v>14610</v>
       </c>
       <c r="L6" t="n">
-        <v>14600</v>
+        <v>16600</v>
       </c>
       <c r="M6" t="n">
-        <v>14120</v>
+        <v>14610</v>
       </c>
       <c r="N6" t="n">
-        <v>9.779999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="O6" t="n">
-        <v>12824684955</v>
+        <v>22452668020</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>30800</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>9810</v>
       </c>
       <c r="R6" t="n">
-        <v>33000</v>
+        <v>31000</v>
       </c>
       <c r="S6" t="n">
-        <v>-2000</v>
+        <v>1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설, 잦은 수주 발표에도 불구하고 주가 하락세 지속. 주가 조작 및 외인 보유율 관련 의혹 제기.</t>
+          <t>하이드로겔 주문 폭증으로 인한 생산 능력 부족 언급. 신규 상장주로서 제2의 에이피알 기대감과 단기 급등 가능성 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['수주', '주가 하락', '주가 조작']</t>
+          <t>['하이드로겔', '신규상장', '주문폭증']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8830</v>
+        <v>14800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.00%</t>
+          <t>'+0.48%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.02</v>
+        <v>-0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H7" t="n">
-        <v>1.74</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9010</v>
+        <v>14730</v>
       </c>
       <c r="K7" t="n">
-        <v>8810</v>
+        <v>14500</v>
       </c>
       <c r="L7" t="n">
-        <v>9500</v>
+        <v>14800</v>
       </c>
       <c r="M7" t="n">
-        <v>8510</v>
+        <v>14120</v>
       </c>
       <c r="N7" t="n">
-        <v>0.72</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>79159331000</v>
+        <v>13950157260</v>
       </c>
       <c r="P7" t="n">
-        <v>9500</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>2270</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-197000</v>
+        <v>33000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>HT로보틱스, 로봇주 강세 속 관심 집중. 향후 주도주 가능성 및 자금 유입 여부 주목.</t>
+          <t>이재명 대통령 관련 정치적 이슈와 연계된 부정적 언급 다수. 주가 조작 및 뱅크런에 대한 의혹 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['로봇주', '주도주', '자금 유입']</t>
+          <t>['대우건설', '이재명', '주가조작']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1243000</v>
+        <v>1258000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.28%</t>
+          <t>'-1.10%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="G8" t="n">
-        <v>1283</v>
+        <v>1252</v>
       </c>
       <c r="H8" t="n">
         <v>48.82</v>
@@ -1162,7 +1162,7 @@
         <v>48.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1510628646000</v>
+        <v>1700462562500</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 우회 상장 이슈로 인한 부정적 여론 형성. 주가 하락 및 경영진 비판.</t>
+          <t>솔리다임 우회상장 철회 요구와 함께 부정적인 전망 제기. 정치적 이슈와 연관된 강한 비판 다수.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['솔리다임', '우회상장', '주가 하락']</t>
+          <t>['솔리다임', '우회상장', '반도체']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1201,6 +1201,98 @@
       <c r="Z8" t="inlineStr">
         <is>
           <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8770</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-2.66%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E9" t="n">
+        <v>45</v>
+      </c>
+      <c r="F9" t="n">
+        <v>31</v>
+      </c>
+      <c r="G9" t="n">
+        <v>92</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>9010</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8810</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9500</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8510</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="O9" t="n">
+        <v>82021395065</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9500</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-197000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>로봇주 강세 속에서 급등 기대감 형성. 개인 투자자 유입과 함께 추가 상승 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['로봇주', '텐배거', '야간선물']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>396300</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261019_10.xlsx
+++ b/data/trending_integrated_20261019_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F2" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>19801112996</v>
+        <v>19905708072</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급 뉴스 확인. 외인 및 국민연금 순매수 동향 포착.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급 계약 체결. 국민연금, 외인 등 기관의 관심 증대. 9~10억 규모의 계약이지만 공시에는 누락됨.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스페이스X', '공급 계약', '외인 매수']</t>
+          <t>['스페이스X', '강관 공급', '국민연금']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9430</v>
+        <v>9440</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.60%</t>
+          <t>'+11.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>17262013215</v>
+        <v>17626941470</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>테슬라 로드스터 수혜주로 언급되며 급등 기대감 존재. 자사주 매입 공시와 함께 주가 상승 가능성 제기.</t>
+          <t>명신산업, 테슬라 로드스터 수혜 기대감 속에서 70% 매출 의존도 언급. 저평가 분석 및 자사주 매입 가능성 제시. 공매도 관련 논의.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['테슬라', '로드스터', '자사주매입']</t>
+          <t>['테슬라', '로드스터', '자사주 매입']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>173900</v>
+        <v>172200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.01%</t>
+          <t>'+2.99%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>317381665500</v>
+        <v>336037092300</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>주문 실수로 인한 혼란 속에서 반등 기대감 형성. 시장 전반의 불안정성과 개인투자자 혼조세.</t>
+          <t>삼성전자우, 주문 실수 논란 속에서 변동성 시현. 우선주 특성으로 인한 급등 가능성과 외인 매수세 관찰. 시장의 주목.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['우선주', '호가창', '시장가']</t>
+          <t>['우선주', '주문 실수', '외인 매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>219500</v>
+        <v>15180</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.86%</t>
+          <t>'+1.54%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>488</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>1347</v>
+        <v>46</v>
       </c>
       <c r="H5" t="n">
-        <v>45.99</v>
+        <v>0.06</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>215500</v>
+        <v>14950</v>
       </c>
       <c r="K5" t="n">
-        <v>207000</v>
+        <v>14610</v>
       </c>
       <c r="L5" t="n">
-        <v>219500</v>
+        <v>16600</v>
       </c>
       <c r="M5" t="n">
-        <v>206500</v>
+        <v>14610</v>
       </c>
       <c r="N5" t="n">
-        <v>45.98</v>
+        <v>0.11</v>
       </c>
       <c r="O5" t="n">
-        <v>1261626249000</v>
+        <v>22846315530</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>30800</v>
       </c>
       <c r="Q5" t="n">
-        <v>94500</v>
+        <v>9810</v>
       </c>
       <c r="R5" t="n">
-        <v>1113000</v>
+        <v>31000</v>
       </c>
       <c r="S5" t="n">
-        <v>504000</v>
+        <v>1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외인 매수에 따른 상승 기대감과 호실적 언급. 다만, 감정적 표현이 많아 객관적 근거는 부족.</t>
+          <t>진코스텍, 하이드로겔 주문 폭증 소식에도 불구하고 주가 하락. 신규 상장주로서의 높은 변동성과 전 고점 돌파 후 하락 가능성 제기. 주가 조작 신고 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['호실적', '외인매수', '공매도']</t>
+          <t>['하이드로겔', '신규상장주', '주가조작']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15090</v>
+        <v>218000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+1.16%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>28</v>
+        <v>501</v>
       </c>
       <c r="G6" t="n">
-        <v>45</v>
+        <v>1348</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06</v>
+        <v>45.99</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14950</v>
+        <v>215500</v>
       </c>
       <c r="K6" t="n">
-        <v>14610</v>
+        <v>207000</v>
       </c>
       <c r="L6" t="n">
-        <v>16600</v>
+        <v>219500</v>
       </c>
       <c r="M6" t="n">
-        <v>14610</v>
+        <v>206500</v>
       </c>
       <c r="N6" t="n">
-        <v>0.11</v>
+        <v>45.98</v>
       </c>
       <c r="O6" t="n">
-        <v>22452668020</v>
+        <v>1346942420000</v>
       </c>
       <c r="P6" t="n">
-        <v>30800</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>9810</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>31000</v>
+        <v>1113000</v>
       </c>
       <c r="S6" t="n">
-        <v>1000</v>
+        <v>504000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>하이드로겔 주문 폭증으로 인한 생산 능력 부족 언급. 신규 상장주로서 제2의 에이피알 기대감과 단기 급등 가능성 제기.</t>
+          <t>삼성전자, 횡보 구간에서의 개인 매도와 외인 매수 관찰. 호실적 및 배당 기대감 존재. 단기 급등 가능성에 대한 논의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['하이드로겔', '신규상장', '주문폭증']</t>
+          <t>['호실적', '외인 매수', '배당']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14800</v>
+        <v>14740</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.48%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="H7" t="n">
         <v>9.699999999999999</v>
@@ -1061,7 +1061,7 @@
         <v>14500</v>
       </c>
       <c r="L7" t="n">
-        <v>14800</v>
+        <v>14840</v>
       </c>
       <c r="M7" t="n">
         <v>14120</v>
@@ -1070,7 +1070,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>13950157260</v>
+        <v>15218556485</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>이재명 대통령 관련 정치적 이슈와 연계된 부정적 언급 다수. 주가 조작 및 뱅크런에 대한 의혹 제기.</t>
+          <t>대우건설, 민주당 정책 및 정치인 언급과 함께 주가 하락세 지속. 뱅크런, 주가 조작 의혹 제기. 수주 발표 시 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['대우건설', '이재명', '주가조작']</t>
+          <t>['민주당', '주가조작', '수주']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1258000</v>
+        <v>1250000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.10%</t>
+          <t>'-1.73%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G8" t="n">
-        <v>1252</v>
+        <v>1220</v>
       </c>
       <c r="H8" t="n">
         <v>48.82</v>
@@ -1162,7 +1162,7 @@
         <v>48.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1700462562500</v>
+        <v>1795189030000</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>솔리다임 우회상장 철회 요구와 함께 부정적인 전망 제기. 정치적 이슈와 연관된 강한 비판 다수.</t>
+          <t>SK하이닉스, 솔리다임 우회 상장 철회 요구 및 정치권 개입 주장. 사생활 문제와 회사 운영 연관성 제기. 공매도 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['솔리다임', '우회상장', '반도체']</t>
+          <t>['솔리다임', '우회상장', '최태원']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8770</v>
+        <v>14690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.66%</t>
+          <t>'-2.13%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="H9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9010</v>
+        <v>15010</v>
       </c>
       <c r="K9" t="n">
-        <v>8810</v>
+        <v>14460</v>
       </c>
       <c r="L9" t="n">
-        <v>9500</v>
+        <v>15160</v>
       </c>
       <c r="M9" t="n">
-        <v>8510</v>
+        <v>13610</v>
       </c>
       <c r="N9" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>82021395065</v>
+        <v>26267983605</v>
       </c>
       <c r="P9" t="n">
-        <v>9500</v>
+        <v>28800</v>
       </c>
       <c r="Q9" t="n">
-        <v>2270</v>
+        <v>13610</v>
       </c>
       <c r="R9" t="n">
-        <v>-197000</v>
+        <v>29000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>로봇주 강세 속에서 급등 기대감 형성. 개인 투자자 유입과 함께 추가 상승 가능성 언급.</t>
+          <t>멜콘, 개잡주 및 상폐 가능성 언급 속에서 주가 하락 우려. 공모가 대비 높은 가격 유지에 대한 의문 제기. 단기 하락 가능성 경고.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['로봇주', '텐배거', '야간선물']</t>
+          <t>['개잡주', '공모가', '상폐']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1291,6 +1291,190 @@
         </is>
       </c>
       <c r="Z9" t="inlineStr">
+        <is>
+          <t>179880</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>17830</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-3.10%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43</v>
+      </c>
+      <c r="F10" t="n">
+        <v>29</v>
+      </c>
+      <c r="G10" t="n">
+        <v>112</v>
+      </c>
+      <c r="H10" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>18400</v>
+      </c>
+      <c r="K10" t="n">
+        <v>17690</v>
+      </c>
+      <c r="L10" t="n">
+        <v>17950</v>
+      </c>
+      <c r="M10" t="n">
+        <v>17670</v>
+      </c>
+      <c r="N10" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="O10" t="n">
+        <v>18700868495</v>
+      </c>
+      <c r="P10" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>17210</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-189000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>삼성중공업, 조선주 전반의 목표가 하향 조정 및 공매도 관련 우려. 반대매매 지속 가능성과 지수 반등에도 오르지 못하는 상황.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['조선주', '공매도', '목표가 하향']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8630</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-4.22%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E11" t="n">
+        <v>54</v>
+      </c>
+      <c r="F11" t="n">
+        <v>36</v>
+      </c>
+      <c r="G11" t="n">
+        <v>102</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>9010</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8810</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9500</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8510</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="O11" t="n">
+        <v>87585562370</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9500</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-197000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>HT로보틱스, 로봇주 관련 관심 속에서 주가 변동성 시현. 개인 투자자들의 참여 및 연말 주도주 가능성 논의. 야간 선물 급락에 따른 시초가 하락 예상.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['로봇주', '주도주', '야간선물']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>396300</t>
         </is>

--- a/data/trending_integrated_20261019_10.xlsx
+++ b/data/trending_integrated_20261019_10.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F2" t="n">
         <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>19905708072</v>
+        <v>19990349728</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급 계약 체결. 국민연금, 외인 등 기관의 관심 증대. 9~10억 규모의 계약이지만 공시에는 누락됨.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 공급 계약 체결. 국민연금 순매수, 외국인 비중 증가.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스페이스X', '강관 공급', '국민연금']</t>
+          <t>['KBI동양철관', '스페이스X', '강관 공급']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>17626941470</v>
+        <v>17985311845</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>명신산업, 테슬라 로드스터 수혜 기대감 속에서 70% 매출 의존도 언급. 저평가 분석 및 자사주 매입 가능성 제시. 공매도 관련 논의.</t>
+          <t>명신산업, 테슬라 로드스터 수혜 기대감 반영. 자사주 매입 및 프로그램 매수세 유입.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['테슬라', '로드스터', '자사주 매입']</t>
+          <t>['명신산업', '테슬라', '로드스터']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>172200</v>
+        <v>171900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+2.81%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>336037092300</v>
+        <v>348098222600</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성전자우, 주문 실수 논란 속에서 변동성 시현. 우선주 특성으로 인한 급등 가능성과 외인 매수세 관찰. 시장의 주목.</t>
+          <t>삼성전자우, 시장 혼조세 속 소폭 상승. 일부 투자자 주문 실수 논란.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['우선주', '주문 실수', '외인 매수']</t>
+          <t>['삼성전자우', '우선주', '시장 혼조']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15180</v>
+        <v>15160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.54%</t>
+          <t>'+1.40%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H5" t="n">
         <v>0.06</v>
@@ -886,7 +886,7 @@
         <v>0.11</v>
       </c>
       <c r="O5" t="n">
-        <v>22846315530</v>
+        <v>23203493390</v>
       </c>
       <c r="P5" t="n">
         <v>30800</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>진코스텍, 하이드로겔 주문 폭증 소식에도 불구하고 주가 하락. 신규 상장주로서의 높은 변동성과 전 고점 돌파 후 하락 가능성 제기. 주가 조작 신고 언급.</t>
+          <t>진코스텍, 하이드로겔 주문 폭증으로 생산 능력 초과. 신규 주문 일부 미수용.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['하이드로겔', '신규상장주', '주가조작']</t>
+          <t>['진코스텍', '하이드로겔', '주문 폭증']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>218000</v>
+        <v>217500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.16%</t>
+          <t>'+0.93%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="G6" t="n">
-        <v>1348</v>
+        <v>1374</v>
       </c>
       <c r="H6" t="n">
         <v>45.99</v>
@@ -978,7 +978,7 @@
         <v>45.98</v>
       </c>
       <c r="O6" t="n">
-        <v>1346942420000</v>
+        <v>1402909371000</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자, 횡보 구간에서의 개인 매도와 외인 매수 관찰. 호실적 및 배당 기대감 존재. 단기 급등 가능성에 대한 논의.</t>
+          <t>삼성전자, 시장 기대감 속 주가 반등 시도. 외인 순매수 및 쌍끌이 매수세 유입.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['호실적', '외인 매수', '배당']</t>
+          <t>['삼성전자', '외인 매수', '주가 반등']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H7" t="n">
         <v>9.699999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>15218556485</v>
+        <v>15892515965</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대우건설, 민주당 정책 및 정치인 언급과 함께 주가 하락세 지속. 뱅크런, 주가 조작 의혹 제기. 수주 발표 시 하락 가능성 언급.</t>
+          <t>대우건설, 주가 하락 및 반등 시도. 정치권 정책 관련 언급 다수.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['민주당', '주가조작', '수주']</t>
+          <t>['대우건설', '주가 하락', '정치권']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1250000</v>
+        <v>1242000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.73%</t>
+          <t>'-2.36%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="G8" t="n">
-        <v>1220</v>
+        <v>1197</v>
       </c>
       <c r="H8" t="n">
         <v>48.82</v>
@@ -1162,7 +1162,7 @@
         <v>48.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1795189030000</v>
+        <v>1880571727500</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 우회 상장 철회 요구 및 정치권 개입 주장. 사생활 문제와 회사 운영 연관성 제기. 공매도 및 주가 하락 우려.</t>
+          <t>SK하이닉스, 솔리다임 우회 상장 철회 요구 다수. 정치권 연루 의혹 및 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['솔리다임', '우회상장', '최태원']</t>
+          <t>['SK하이닉스', '솔리다임', '우회상장']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14690</v>
+        <v>14570</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.13%</t>
+          <t>'-2.93%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1245,7 +1245,7 @@
         <v>14460</v>
       </c>
       <c r="L9" t="n">
-        <v>15160</v>
+        <v>15200</v>
       </c>
       <c r="M9" t="n">
         <v>13610</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>26267983605</v>
+        <v>30292689580</v>
       </c>
       <c r="P9" t="n">
         <v>28800</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>멜콘, 개잡주 및 상폐 가능성 언급 속에서 주가 하락 우려. 공모가 대비 높은 가격 유지에 대한 의문 제기. 단기 하락 가능성 경고.</t>
+          <t>멜콘, 주가 하락 및 투자자 이탈. 공모가 아래로 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['개잡주', '공모가', '상폐']</t>
+          <t>['멜콘', '주가 하락', '공모가']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17830</v>
+        <v>17840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.10%</t>
+          <t>'-3.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>18700868495</v>
+        <v>19633253380</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>삼성중공업, 조선주 전반의 목표가 하향 조정 및 공매도 관련 우려. 반대매매 지속 가능성과 지수 반등에도 오르지 못하는 상황.</t>
+          <t>삼성중공업, 주가 하락세 지속. 조선업종 목표가 하향 조정 및 공매도 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['조선주', '공매도', '목표가 하향']</t>
+          <t>['삼성중공업', '주가 하락', '공매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8630</v>
+        <v>8650</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.22%</t>
+          <t>'-4.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1.02</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="H11" t="n">
         <v>1.74</v>
@@ -1438,7 +1438,7 @@
         <v>0.72</v>
       </c>
       <c r="O11" t="n">
-        <v>87585562370</v>
+        <v>89822124020</v>
       </c>
       <c r="P11" t="n">
         <v>9500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>HT로보틱스, 로봇주 관련 관심 속에서 주가 변동성 시현. 개인 투자자들의 참여 및 연말 주도주 가능성 논의. 야간 선물 급락에 따른 시초가 하락 예상.</t>
+          <t>HT로보틱스, 로봇주로서 시장 관심. 주가 변동성 및 투자자들의 기대감 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['로봇주', '주도주', '야간선물']</t>
+          <t>['HT로보틱스', '로봇주', '시장 관심']</t>
         </is>
       </c>
       <c r="X11" t="n">

--- a/data/trending_integrated_20261019_10.xlsx
+++ b/data/trending_integrated_20261019_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2" t="n">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>19990349728</v>
+        <v>20080368232</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 공급 계약 체결. 국민연금 순매수, 외국인 비중 증가.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 950톤 공급 단독 보도. 4월부터 납품 시작 확인.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['KBI동양철관', '스페이스X', '강관 공급']</t>
+          <t>['스페이스X', '강관', '단독']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9440</v>
+        <v>9370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.72%</t>
+          <t>'+10.89%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
         <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>17985311845</v>
+        <v>18358211560</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>171900</v>
+        <v>170600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.81%</t>
+          <t>'+2.03%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>348098222600</v>
+        <v>362491791500</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성전자우, 시장 혼조세 속 소폭 상승. 일부 투자자 주문 실수 논란.</t>
+          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['삼성전자우', '우선주', '시장 혼조']</t>
+          <t>['우선주', '주문실수', '외인매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,70 +839,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15160</v>
+        <v>216250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.40%</t>
+          <t>'+0.35%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>493</v>
       </c>
       <c r="G5" t="n">
-        <v>47</v>
+        <v>1391</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06</v>
+        <v>45.99</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14950</v>
+        <v>215500</v>
       </c>
       <c r="K5" t="n">
-        <v>14610</v>
+        <v>207000</v>
       </c>
       <c r="L5" t="n">
-        <v>16600</v>
+        <v>219500</v>
       </c>
       <c r="M5" t="n">
-        <v>14610</v>
+        <v>206500</v>
       </c>
       <c r="N5" t="n">
-        <v>0.11</v>
+        <v>45.98</v>
       </c>
       <c r="O5" t="n">
-        <v>23203493390</v>
+        <v>1443882871750</v>
       </c>
       <c r="P5" t="n">
-        <v>30800</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>9810</v>
+        <v>94500</v>
       </c>
       <c r="R5" t="n">
-        <v>31000</v>
+        <v>1113000</v>
       </c>
       <c r="S5" t="n">
-        <v>1000</v>
+        <v>504000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>진코스텍, 하이드로겔 주문 폭증으로 생산 능력 초과. 신규 주문 일부 미수용.</t>
+          <t>삼성전자, 호실적 및 낮은 PER 기반 상승 기대감 존재. 외인 매수세 유입 관측.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['진코스텍', '하이드로겔', '주문 폭증']</t>
+          <t>['호실적', 'PER', '외인매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>217500</v>
+        <v>14950</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.93%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
-        <v>496</v>
+        <v>28</v>
       </c>
       <c r="G6" t="n">
-        <v>1374</v>
+        <v>49</v>
       </c>
       <c r="H6" t="n">
-        <v>45.99</v>
+        <v>0.06</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>215500</v>
+        <v>14950</v>
       </c>
       <c r="K6" t="n">
-        <v>207000</v>
+        <v>14610</v>
       </c>
       <c r="L6" t="n">
-        <v>219500</v>
+        <v>16600</v>
       </c>
       <c r="M6" t="n">
-        <v>206500</v>
+        <v>14610</v>
       </c>
       <c r="N6" t="n">
-        <v>45.98</v>
+        <v>0.11</v>
       </c>
       <c r="O6" t="n">
-        <v>1402909371000</v>
+        <v>23796270380</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>30800</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>9810</v>
       </c>
       <c r="R6" t="n">
-        <v>1113000</v>
+        <v>31000</v>
       </c>
       <c r="S6" t="n">
-        <v>504000</v>
+        <v>1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자, 시장 기대감 속 주가 반등 시도. 외인 순매수 및 쌍끌이 매수세 유입.</t>
+          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['삼성전자', '외인 매수', '주가 반등']</t>
+          <t>['하이드로겔', '주문폭증', '신규주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14740</v>
+        <v>14660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'-0.48%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1070,7 +1070,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>15892515965</v>
+        <v>16601635350</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1242000</v>
+        <v>1235000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.36%</t>
+          <t>'-2.91%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G8" t="n">
-        <v>1197</v>
+        <v>1219</v>
       </c>
       <c r="H8" t="n">
         <v>48.82</v>
@@ -1162,7 +1162,7 @@
         <v>48.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1880571727500</v>
+        <v>1948345220500</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 우회 상장 철회 요구 다수. 정치권 연루 의혹 및 주가 하락 우려.</t>
+          <t>SK하이닉스, 솔리다임 우회상장 철회 요구 거세. 정치권 개입 및 부정적 전망 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '솔리다임', '우회상장']</t>
+          <t>['솔리다임', '우회상장', '최태원']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14570</v>
+        <v>17780</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.93%</t>
+          <t>'-3.37%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>27.85</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>15010</v>
+        <v>18400</v>
       </c>
       <c r="K9" t="n">
-        <v>14460</v>
+        <v>17690</v>
       </c>
       <c r="L9" t="n">
-        <v>15200</v>
+        <v>17950</v>
       </c>
       <c r="M9" t="n">
-        <v>13610</v>
+        <v>17670</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>27.77</v>
       </c>
       <c r="O9" t="n">
-        <v>30292689580</v>
+        <v>20923827125</v>
       </c>
       <c r="P9" t="n">
-        <v>28800</v>
+        <v>35350</v>
       </c>
       <c r="Q9" t="n">
-        <v>13610</v>
+        <v>17210</v>
       </c>
       <c r="R9" t="n">
-        <v>29000</v>
+        <v>-189000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>멜콘, 주가 하락 및 투자자 이탈. 공모가 아래로 하락 가능성 언급.</t>
+          <t>삼성중공업, 조선주 목표가 하향 조정 및 공매도 지속. 하락세 지속 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['멜콘', '주가 하락', '공모가']</t>
+          <t>['조선주', '공매도', '목표가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17840</v>
+        <v>8580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.04%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>1.02</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="H10" t="n">
-        <v>27.85</v>
+        <v>1.74</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18400</v>
+        <v>9010</v>
       </c>
       <c r="K10" t="n">
-        <v>17690</v>
+        <v>8810</v>
       </c>
       <c r="L10" t="n">
-        <v>17950</v>
+        <v>9500</v>
       </c>
       <c r="M10" t="n">
-        <v>17670</v>
+        <v>8510</v>
       </c>
       <c r="N10" t="n">
-        <v>27.77</v>
+        <v>0.72</v>
       </c>
       <c r="O10" t="n">
-        <v>19633253380</v>
+        <v>91451458390</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>9500</v>
       </c>
       <c r="Q10" t="n">
-        <v>17210</v>
+        <v>2270</v>
       </c>
       <c r="R10" t="n">
-        <v>-189000</v>
+        <v>-197000</v>
       </c>
       <c r="S10" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>삼성중공업, 주가 하락세 지속. 조선업종 목표가 하향 조정 및 공매도 우려.</t>
+          <t>HT로보틱스, 로봇주 강세 속 주가 변동성 관측. 연말 주도주 가능성 탐색.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['삼성중공업', '주가 하락', '공매도']</t>
+          <t>['로봇주', '주도주', '변동성']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8650</v>
+        <v>14200</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.00%</t>
+          <t>'-5.40%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="H11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>9010</v>
+        <v>15010</v>
       </c>
       <c r="K11" t="n">
-        <v>8810</v>
+        <v>14460</v>
       </c>
       <c r="L11" t="n">
-        <v>9500</v>
+        <v>15200</v>
       </c>
       <c r="M11" t="n">
-        <v>8510</v>
+        <v>13610</v>
       </c>
       <c r="N11" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>89822124020</v>
+        <v>32331184780</v>
       </c>
       <c r="P11" t="n">
-        <v>9500</v>
+        <v>28800</v>
       </c>
       <c r="Q11" t="n">
-        <v>2270</v>
+        <v>13610</v>
       </c>
       <c r="R11" t="n">
-        <v>-197000</v>
+        <v>29000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>HT로보틱스, 로봇주로서 시장 관심. 주가 변동성 및 투자자들의 기대감 혼재.</t>
+          <t>멜콘, 과거 거래 이력 및 주포 활동 분석. 투자 주의 의견 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['HT로보틱스', '로봇주', '시장 관심']</t>
+          <t>['주포', '거래량', '투자주의']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,7 +1476,99 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>179880</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TS트릴리온</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1180</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-6.42%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1261</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1301</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1339</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1145</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8876318944</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1950</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>192</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-264000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>TS트릴리온, 데이터센터 건립 호재에도 불구하고 주가 부진. 동전주 탈출 기대.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['데이터센터', 'AI', '성장성']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>317240</t>
         </is>
       </c>
     </row>
